--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-10).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-10).xlsx
@@ -935,94 +935,91 @@
     <t>214</t>
   </si>
   <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>R$ 8.705,66</t>
-  </si>
-  <si>
-    <t>91.4</t>
-  </si>
-  <si>
-    <t>56.8</t>
-  </si>
-  <si>
-    <t>6.04</t>
-  </si>
-  <si>
-    <t>20.6</t>
-  </si>
-  <si>
-    <t>7.9</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>42.0%</t>
-  </si>
-  <si>
-    <t>16.4%</t>
+    <t>33</t>
+  </si>
+  <si>
+    <t>R$ 8.662,59</t>
+  </si>
+  <si>
+    <t>91.0</t>
+  </si>
+  <si>
+    <t>56.9</t>
+  </si>
+  <si>
+    <t>6.10</t>
+  </si>
+  <si>
+    <t>20.8</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>37.6%</t>
+  </si>
+  <si>
+    <t>17.1%</t>
   </si>
   <si>
     <t>1.4%</t>
   </si>
   <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>3.2%</t>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>3.3%</t>
   </si>
   <si>
     <t>1.1%</t>
   </si>
   <si>
-    <t>0.2%</t>
-  </si>
-  <si>
     <t>5.8%</t>
   </si>
   <si>
     <t>2.8%</t>
   </si>
   <si>
-    <t>5.0%</t>
-  </si>
-  <si>
-    <t>1831.0</t>
-  </si>
-  <si>
-    <t>1522.0</t>
-  </si>
-  <si>
-    <t>125.0</t>
-  </si>
-  <si>
-    <t>13.0</t>
-  </si>
-  <si>
-    <t>298.0</t>
-  </si>
-  <si>
-    <t>100.0</t>
-  </si>
-  <si>
-    <t>15.0</t>
-  </si>
-  <si>
-    <t>539.0</t>
-  </si>
-  <si>
-    <t>259.0</t>
-  </si>
-  <si>
-    <t>460.0</t>
+    <t>5.5%</t>
+  </si>
+  <si>
+    <t>2109.0</t>
+  </si>
+  <si>
+    <t>1768.0</t>
+  </si>
+  <si>
+    <t>140.0</t>
+  </si>
+  <si>
+    <t>19.0</t>
+  </si>
+  <si>
+    <t>341.0</t>
+  </si>
+  <si>
+    <t>109.0</t>
+  </si>
+  <si>
+    <t>18.0</t>
+  </si>
+  <si>
+    <t>606.0</t>
+  </si>
+  <si>
+    <t>285.0</t>
+  </si>
+  <si>
+    <t>573.0</t>
   </si>
   <si>
     <t>0.4%</t>
   </si>
   <si>
-    <t>35.0</t>
+    <t>37.0</t>
   </si>
   <si>
     <t>1</t>
@@ -5096,7 +5093,9 @@
       <c r="N25" s="6">
         <v>139</v>
       </c>
-      <c r="O25" s="6"/>
+      <c r="O25" s="6">
+        <v>91</v>
+      </c>
       <c r="P25" s="7">
         <v>11.34553115942029</v>
       </c>
@@ -5106,31 +5105,75 @@
       <c r="R25" s="8">
         <v>11.091574725274725</v>
       </c>
-      <c r="S25" s="8"/>
+      <c r="S25" s="8">
+        <v>7</v>
+      </c>
       <c r="T25" s="9">
         <v>0.10989010989010989</v>
       </c>
-      <c r="U25" s="9"/>
-      <c r="V25" s="9"/>
-      <c r="W25" s="9"/>
-      <c r="X25" s="9"/>
-      <c r="Y25" s="9"/>
-      <c r="Z25" s="9"/>
-      <c r="AA25" s="9"/>
-      <c r="AB25" s="9"/>
-      <c r="AC25" s="9"/>
-      <c r="AD25" s="6"/>
-      <c r="AE25" s="6"/>
-      <c r="AF25" s="6"/>
-      <c r="AG25" s="6"/>
-      <c r="AH25" s="6"/>
-      <c r="AI25" s="6"/>
-      <c r="AJ25" s="6"/>
-      <c r="AK25" s="6"/>
-      <c r="AL25" s="6"/>
-      <c r="AM25" s="6"/>
-      <c r="AN25" s="9"/>
-      <c r="AO25" s="6"/>
+      <c r="U25" s="9">
+        <v>0.16483516483516483</v>
+      </c>
+      <c r="V25" s="9">
+        <v>0</v>
+      </c>
+      <c r="W25" s="9">
+        <v>0</v>
+      </c>
+      <c r="X25" s="9">
+        <v>0.02197802197802198</v>
+      </c>
+      <c r="Y25" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="9">
+        <v>0.02197802197802198</v>
+      </c>
+      <c r="AC25" s="9">
+        <v>0.13186813186813187</v>
+      </c>
+      <c r="AD25" s="6">
+        <v>16</v>
+      </c>
+      <c r="AE25" s="6">
+        <v>15</v>
+      </c>
+      <c r="AF25" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI25" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM25" s="6">
+        <v>12</v>
+      </c>
+      <c r="AN25" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP25" s="4">
         <v>58</v>
       </c>
@@ -5992,7 +6035,9 @@
       <c r="N31" s="6">
         <v>62</v>
       </c>
-      <c r="O31" s="6"/>
+      <c r="O31" s="6">
+        <v>42</v>
+      </c>
       <c r="P31" s="7">
         <v>5.7570312499999998</v>
       </c>
@@ -6002,31 +6047,75 @@
       <c r="R31" s="8">
         <v>11.494840476190475</v>
       </c>
-      <c r="S31" s="8"/>
+      <c r="S31" s="8">
+        <v>8</v>
+      </c>
       <c r="T31" s="9">
         <v>0.21428571428571427</v>
       </c>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="9"/>
-      <c r="Z31" s="9"/>
-      <c r="AA31" s="9"/>
-      <c r="AB31" s="9"/>
-      <c r="AC31" s="9"/>
-      <c r="AD31" s="6"/>
-      <c r="AE31" s="6"/>
-      <c r="AF31" s="6"/>
-      <c r="AG31" s="6"/>
-      <c r="AH31" s="6"/>
-      <c r="AI31" s="6"/>
-      <c r="AJ31" s="6"/>
-      <c r="AK31" s="6"/>
-      <c r="AL31" s="6"/>
-      <c r="AM31" s="6"/>
-      <c r="AN31" s="9"/>
-      <c r="AO31" s="6"/>
+      <c r="U31" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="V31" s="9">
+        <v>0.023809523809523808</v>
+      </c>
+      <c r="W31" s="9">
+        <v>0</v>
+      </c>
+      <c r="X31" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="AC31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE31" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF31" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP31" s="4">
         <v>58</v>
       </c>
@@ -7082,7 +7171,9 @@
       <c r="N39" s="6">
         <v>99</v>
       </c>
-      <c r="O39" s="6"/>
+      <c r="O39" s="6">
+        <v>65</v>
+      </c>
       <c r="P39" s="7">
         <v>2.0920878787878787</v>
       </c>
@@ -7092,31 +7183,75 @@
       <c r="R39" s="8">
         <v>6.6144803278688524</v>
       </c>
-      <c r="S39" s="8"/>
+      <c r="S39" s="8">
+        <v>8</v>
+      </c>
       <c r="T39" s="9">
         <v>0.43076923076923079</v>
       </c>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="6"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
-      <c r="AH39" s="6"/>
-      <c r="AI39" s="6"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="6"/>
-      <c r="AL39" s="6"/>
-      <c r="AM39" s="6"/>
-      <c r="AN39" s="9"/>
-      <c r="AO39" s="6"/>
+      <c r="U39" s="9">
+        <v>0.33846153846153848</v>
+      </c>
+      <c r="V39" s="9">
+        <v>0.015384615384615385</v>
+      </c>
+      <c r="W39" s="9">
+        <v>0.015384615383999999</v>
+      </c>
+      <c r="X39" s="9">
+        <v>0.2153846153846154</v>
+      </c>
+      <c r="Y39" s="9">
+        <v>0.030769230769230771</v>
+      </c>
+      <c r="Z39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="9">
+        <v>0.092307692307692313</v>
+      </c>
+      <c r="AB39" s="9">
+        <v>0.1076923076923077</v>
+      </c>
+      <c r="AC39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="6">
+        <v>30</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>22</v>
+      </c>
+      <c r="AF39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH39" s="6">
+        <v>14</v>
+      </c>
+      <c r="AI39" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="6">
+        <v>6</v>
+      </c>
+      <c r="AL39" s="6">
+        <v>7</v>
+      </c>
+      <c r="AM39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP39" s="4">
         <v>58</v>
       </c>
@@ -7507,7 +7642,9 @@
       <c r="N42" s="6">
         <v>88</v>
       </c>
-      <c r="O42" s="6"/>
+      <c r="O42" s="6">
+        <v>73</v>
+      </c>
       <c r="P42" s="7">
         <v>7.2955430232558136</v>
       </c>
@@ -7517,31 +7654,75 @@
       <c r="R42" s="8">
         <v>11.85891971830986</v>
       </c>
-      <c r="S42" s="8"/>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
       <c r="T42" s="9">
         <v>0.20547945205479451</v>
       </c>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="U42" s="9">
+        <v>0.082191780821917804</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0.013698630136986301</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0.013698630136986301</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.068493150684931503</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -8244,7 +8425,9 @@
       <c r="N47" s="6">
         <v>240</v>
       </c>
-      <c r="O47" s="6"/>
+      <c r="O47" s="6">
+        <v>119</v>
+      </c>
       <c r="P47" s="7">
         <v>7.99237668161435</v>
       </c>
@@ -8254,31 +8437,75 @@
       <c r="R47" s="8">
         <v>10.240661206896551</v>
       </c>
-      <c r="S47" s="8"/>
+      <c r="S47" s="8">
+        <v>7</v>
+      </c>
       <c r="T47" s="9">
         <v>0.092436974789915971</v>
       </c>
-      <c r="U47" s="9"/>
-      <c r="V47" s="9"/>
-      <c r="W47" s="9"/>
-      <c r="X47" s="9"/>
-      <c r="Y47" s="9"/>
-      <c r="Z47" s="9"/>
-      <c r="AA47" s="9"/>
-      <c r="AB47" s="9"/>
-      <c r="AC47" s="9"/>
-      <c r="AD47" s="6"/>
-      <c r="AE47" s="6"/>
-      <c r="AF47" s="6"/>
-      <c r="AG47" s="6"/>
-      <c r="AH47" s="6"/>
-      <c r="AI47" s="6"/>
-      <c r="AJ47" s="6"/>
-      <c r="AK47" s="6"/>
-      <c r="AL47" s="6"/>
-      <c r="AM47" s="6"/>
-      <c r="AN47" s="9"/>
-      <c r="AO47" s="6"/>
+      <c r="U47" s="9">
+        <v>0.067226890756302518</v>
+      </c>
+      <c r="V47" s="9">
+        <v>0</v>
+      </c>
+      <c r="W47" s="9">
+        <v>0</v>
+      </c>
+      <c r="X47" s="9">
+        <v>0.025210084033613446</v>
+      </c>
+      <c r="Y47" s="9">
+        <v>0.0084033613445378148</v>
+      </c>
+      <c r="Z47" s="9">
+        <v>0.0084033613445378148</v>
+      </c>
+      <c r="AA47" s="9">
+        <v>0.025210084033613446</v>
+      </c>
+      <c r="AB47" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE47" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF47" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI47" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ47" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK47" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL47" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM47" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN47" s="9">
+        <v>0.01680672268907563</v>
+      </c>
+      <c r="AO47" s="6">
+        <v>2</v>
+      </c>
       <c t="s" r="AP47" s="4">
         <v>58</v>
       </c>
@@ -9233,7 +9460,9 @@
       <c r="N54" s="6">
         <v>95</v>
       </c>
-      <c r="O54" s="6"/>
+      <c r="O54" s="6">
+        <v>68</v>
+      </c>
       <c r="P54" s="7">
         <v>5.7842105263157899</v>
       </c>
@@ -9243,31 +9472,75 @@
       <c r="R54" s="8">
         <v>8.335353030303029</v>
       </c>
-      <c r="S54" s="8"/>
+      <c r="S54" s="8">
+        <v>7</v>
+      </c>
       <c r="T54" s="9">
         <v>0.23529411764705882</v>
       </c>
-      <c r="U54" s="9"/>
-      <c r="V54" s="9"/>
-      <c r="W54" s="9"/>
-      <c r="X54" s="9"/>
-      <c r="Y54" s="9"/>
-      <c r="Z54" s="9"/>
-      <c r="AA54" s="9"/>
-      <c r="AB54" s="9"/>
-      <c r="AC54" s="9"/>
-      <c r="AD54" s="6"/>
-      <c r="AE54" s="6"/>
-      <c r="AF54" s="6"/>
-      <c r="AG54" s="6"/>
-      <c r="AH54" s="6"/>
-      <c r="AI54" s="6"/>
-      <c r="AJ54" s="6"/>
-      <c r="AK54" s="6"/>
-      <c r="AL54" s="6"/>
-      <c r="AM54" s="6"/>
-      <c r="AN54" s="9"/>
-      <c r="AO54" s="6"/>
+      <c r="U54" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="V54" s="9">
+        <v>0.014705882352941176</v>
+      </c>
+      <c r="W54" s="9">
+        <v>0</v>
+      </c>
+      <c r="X54" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="Y54" s="9">
+        <v>0.014705882352941176</v>
+      </c>
+      <c r="Z54" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AB54" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE54" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF54" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI54" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN54" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO54" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP54" s="4">
         <v>58</v>
       </c>
@@ -9344,7 +9617,9 @@
       <c r="N55" s="6">
         <v>102</v>
       </c>
-      <c r="O55" s="6"/>
+      <c r="O55" s="6">
+        <v>93</v>
+      </c>
       <c r="P55" s="7">
         <v>2.7903669724770639</v>
       </c>
@@ -9354,31 +9629,75 @@
       <c r="R55" s="8">
         <v>14.599634065934067</v>
       </c>
-      <c r="S55" s="8"/>
+      <c r="S55" s="8">
+        <v>7</v>
+      </c>
       <c r="T55" s="9">
         <v>0.17582417582417584</v>
       </c>
-      <c r="U55" s="9"/>
-      <c r="V55" s="9"/>
-      <c r="W55" s="9"/>
-      <c r="X55" s="9"/>
-      <c r="Y55" s="9"/>
-      <c r="Z55" s="9"/>
-      <c r="AA55" s="9"/>
-      <c r="AB55" s="9"/>
-      <c r="AC55" s="9"/>
-      <c r="AD55" s="6"/>
-      <c r="AE55" s="6"/>
-      <c r="AF55" s="6"/>
-      <c r="AG55" s="6"/>
-      <c r="AH55" s="6"/>
-      <c r="AI55" s="6"/>
-      <c r="AJ55" s="6"/>
-      <c r="AK55" s="6"/>
-      <c r="AL55" s="6"/>
-      <c r="AM55" s="6"/>
-      <c r="AN55" s="9"/>
-      <c r="AO55" s="6"/>
+      <c r="U55" s="9">
+        <v>0.13978494623655913</v>
+      </c>
+      <c r="V55" s="9">
+        <v>0</v>
+      </c>
+      <c r="W55" s="9">
+        <v>0</v>
+      </c>
+      <c r="X55" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="Y55" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="9">
+        <v>0.010752688172043012</v>
+      </c>
+      <c r="AA55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="9">
+        <v>0.086021505376344093</v>
+      </c>
+      <c r="AD55" s="6">
+        <v>15</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM55" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP55" s="4">
         <v>58</v>
       </c>
@@ -10333,7 +10652,9 @@
       <c r="N62" s="6">
         <v>99</v>
       </c>
-      <c r="O62" s="6"/>
+      <c r="O62" s="6">
+        <v>53</v>
+      </c>
       <c r="P62" s="7">
         <v>2.9753468750000001</v>
       </c>
@@ -10343,31 +10664,75 @@
       <c r="R62" s="8">
         <v>3.6254716981132078</v>
       </c>
-      <c r="S62" s="8"/>
+      <c r="S62" s="8">
+        <v>7</v>
+      </c>
       <c r="T62" s="9">
         <v>0.67924528301886788</v>
       </c>
-      <c r="U62" s="9"/>
-      <c r="V62" s="9"/>
-      <c r="W62" s="9"/>
-      <c r="X62" s="9"/>
-      <c r="Y62" s="9"/>
-      <c r="Z62" s="9"/>
-      <c r="AA62" s="9"/>
-      <c r="AB62" s="9"/>
-      <c r="AC62" s="9"/>
-      <c r="AD62" s="6"/>
-      <c r="AE62" s="6"/>
-      <c r="AF62" s="6"/>
-      <c r="AG62" s="6"/>
-      <c r="AH62" s="6"/>
-      <c r="AI62" s="6"/>
-      <c r="AJ62" s="6"/>
-      <c r="AK62" s="6"/>
-      <c r="AL62" s="6"/>
-      <c r="AM62" s="6"/>
-      <c r="AN62" s="9"/>
-      <c r="AO62" s="6"/>
+      <c r="U62" s="9">
+        <v>0.094339622641509441</v>
+      </c>
+      <c r="V62" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="W62" s="9">
+        <v>0</v>
+      </c>
+      <c r="X62" s="9">
+        <v>0.018867924528301886</v>
+      </c>
+      <c r="Y62" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="9">
+        <v>0.056603773584905662</v>
+      </c>
+      <c r="AC62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE62" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF62" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL62" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO62" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP62" s="4">
         <v>58</v>
       </c>
@@ -14392,7 +14757,7 @@
         <v>0.047058823529411764</v>
       </c>
       <c r="W90" s="9">
-        <v>0</v>
+        <v>0.011764705881999999</v>
       </c>
       <c r="X90" s="9">
         <v>0</v>
@@ -14422,7 +14787,7 @@
         <v>4</v>
       </c>
       <c r="AG90" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH90" s="6">
         <v>0</v>
@@ -16147,7 +16512,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16177,35 +16542,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>5402.1499999999996</v>
+      </c>
+      <c r="N102" s="6">
+        <v>57</v>
+      </c>
+      <c r="O102" s="6">
+        <v>41</v>
+      </c>
+      <c r="P102" s="7">
+        <v>12.758333928571428</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>35.969919512195119</v>
+      </c>
+      <c r="R102" s="8">
+        <v>17.325641025641026</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.21951219512195122</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0.024390243902000001</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0.17073170731707318</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>7</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -17162,7 +17585,9 @@
       <c r="N109" s="6">
         <v>141</v>
       </c>
-      <c r="O109" s="6"/>
+      <c r="O109" s="6">
+        <v>41</v>
+      </c>
       <c r="P109" s="7">
         <v>11.66386923076923</v>
       </c>
@@ -17172,31 +17597,75 @@
       <c r="R109" s="8">
         <v>12.349187804878049</v>
       </c>
-      <c r="S109" s="8"/>
+      <c r="S109" s="8">
+        <v>8</v>
+      </c>
       <c r="T109" s="9">
         <v>0.073170731707317069</v>
       </c>
-      <c r="U109" s="9"/>
-      <c r="V109" s="9"/>
-      <c r="W109" s="9"/>
-      <c r="X109" s="9"/>
-      <c r="Y109" s="9"/>
-      <c r="Z109" s="9"/>
-      <c r="AA109" s="9"/>
-      <c r="AB109" s="9"/>
-      <c r="AC109" s="9"/>
-      <c r="AD109" s="6"/>
-      <c r="AE109" s="6"/>
-      <c r="AF109" s="6"/>
-      <c r="AG109" s="6"/>
-      <c r="AH109" s="6"/>
-      <c r="AI109" s="6"/>
-      <c r="AJ109" s="6"/>
-      <c r="AK109" s="6"/>
-      <c r="AL109" s="6"/>
-      <c r="AM109" s="6"/>
-      <c r="AN109" s="9"/>
-      <c r="AO109" s="6"/>
+      <c r="U109" s="9">
+        <v>0.43902439024390244</v>
+      </c>
+      <c r="V109" s="9">
+        <v>0.14634146341463414</v>
+      </c>
+      <c r="W109" s="9">
+        <v>0</v>
+      </c>
+      <c r="X109" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB109" s="9">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="AC109" s="9">
+        <v>0.24390243902439024</v>
+      </c>
+      <c r="AD109" s="6">
+        <v>18</v>
+      </c>
+      <c r="AE109" s="6">
+        <v>18</v>
+      </c>
+      <c r="AF109" s="6">
+        <v>6</v>
+      </c>
+      <c r="AG109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL109" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM109" s="6">
+        <v>10</v>
+      </c>
+      <c r="AN109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO109" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP109" s="4">
         <v>58</v>
       </c>
@@ -18349,7 +18818,9 @@
       <c r="N118" s="6">
         <v>142</v>
       </c>
-      <c r="O118" s="6"/>
+      <c r="O118" s="6">
+        <v>52</v>
+      </c>
       <c r="P118" s="7">
         <v>7.1996093749999996</v>
       </c>
@@ -18359,31 +18830,75 @@
       <c r="R118" s="8">
         <v>9.7570914893617022</v>
       </c>
-      <c r="S118" s="8"/>
+      <c r="S118" s="8">
+        <v>7</v>
+      </c>
       <c r="T118" s="9">
         <v>0.25</v>
       </c>
-      <c r="U118" s="9"/>
-      <c r="V118" s="9"/>
-      <c r="W118" s="9"/>
-      <c r="X118" s="9"/>
-      <c r="Y118" s="9"/>
-      <c r="Z118" s="9"/>
-      <c r="AA118" s="9"/>
-      <c r="AB118" s="9"/>
-      <c r="AC118" s="9"/>
-      <c r="AD118" s="6"/>
-      <c r="AE118" s="6"/>
-      <c r="AF118" s="6"/>
-      <c r="AG118" s="6"/>
-      <c r="AH118" s="6"/>
-      <c r="AI118" s="6"/>
-      <c r="AJ118" s="6"/>
-      <c r="AK118" s="6"/>
-      <c r="AL118" s="6"/>
-      <c r="AM118" s="6"/>
-      <c r="AN118" s="9"/>
-      <c r="AO118" s="6"/>
+      <c r="U118" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="V118" s="9">
+        <v>0</v>
+      </c>
+      <c r="W118" s="9">
+        <v>0</v>
+      </c>
+      <c r="X118" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y118" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z118" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA118" s="9">
+        <v>0.11538461538461539</v>
+      </c>
+      <c r="AB118" s="9">
+        <v>0.096153846153846159</v>
+      </c>
+      <c r="AC118" s="9">
+        <v>0.34615384615384615</v>
+      </c>
+      <c r="AD118" s="6">
+        <v>29</v>
+      </c>
+      <c r="AE118" s="6">
+        <v>26</v>
+      </c>
+      <c r="AF118" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG118" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH118" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI118" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ118" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK118" s="6">
+        <v>6</v>
+      </c>
+      <c r="AL118" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM118" s="6">
+        <v>18</v>
+      </c>
+      <c r="AN118" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO118" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP118" s="4">
         <v>58</v>
       </c>
@@ -24885,7 +25400,9 @@
       <c r="N162" s="6">
         <v>153</v>
       </c>
-      <c r="O162" s="6"/>
+      <c r="O162" s="6">
+        <v>60</v>
+      </c>
       <c r="P162" s="7">
         <v>12.177699295774648</v>
       </c>
@@ -24895,31 +25412,75 @@
       <c r="R162" s="8">
         <v>3.6594449999999998</v>
       </c>
-      <c r="S162" s="8"/>
+      <c r="S162" s="8">
+        <v>8</v>
+      </c>
       <c r="T162" s="9">
         <v>0.033333333333333333</v>
       </c>
-      <c r="U162" s="9"/>
-      <c r="V162" s="9"/>
-      <c r="W162" s="9"/>
-      <c r="X162" s="9"/>
-      <c r="Y162" s="9"/>
-      <c r="Z162" s="9"/>
-      <c r="AA162" s="9"/>
-      <c r="AB162" s="9"/>
-      <c r="AC162" s="9"/>
-      <c r="AD162" s="6"/>
-      <c r="AE162" s="6"/>
-      <c r="AF162" s="6"/>
-      <c r="AG162" s="6"/>
-      <c r="AH162" s="6"/>
-      <c r="AI162" s="6"/>
-      <c r="AJ162" s="6"/>
-      <c r="AK162" s="6"/>
-      <c r="AL162" s="6"/>
-      <c r="AM162" s="6"/>
-      <c r="AN162" s="9"/>
-      <c r="AO162" s="6"/>
+      <c r="U162" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="V162" s="9">
+        <v>0</v>
+      </c>
+      <c r="W162" s="9">
+        <v>0</v>
+      </c>
+      <c r="X162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC162" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AD162" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM162" s="6">
+        <v>10</v>
+      </c>
+      <c r="AN162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO162" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP162" s="4">
         <v>58</v>
       </c>
@@ -24996,7 +25557,9 @@
       <c r="N163" s="6">
         <v>121</v>
       </c>
-      <c r="O163" s="6"/>
+      <c r="O163" s="6">
+        <v>93</v>
+      </c>
       <c r="P163" s="7">
         <v>5.0600577586206894</v>
       </c>
@@ -25006,31 +25569,75 @@
       <c r="R163" s="8">
         <v>8.8617420454545464</v>
       </c>
-      <c r="S163" s="8"/>
+      <c r="S163" s="8">
+        <v>8</v>
+      </c>
       <c r="T163" s="9">
         <v>0.23655913978494625</v>
       </c>
-      <c r="U163" s="9"/>
-      <c r="V163" s="9"/>
-      <c r="W163" s="9"/>
-      <c r="X163" s="9"/>
-      <c r="Y163" s="9"/>
-      <c r="Z163" s="9"/>
-      <c r="AA163" s="9"/>
-      <c r="AB163" s="9"/>
-      <c r="AC163" s="9"/>
-      <c r="AD163" s="6"/>
-      <c r="AE163" s="6"/>
-      <c r="AF163" s="6"/>
-      <c r="AG163" s="6"/>
-      <c r="AH163" s="6"/>
-      <c r="AI163" s="6"/>
-      <c r="AJ163" s="6"/>
-      <c r="AK163" s="6"/>
-      <c r="AL163" s="6"/>
-      <c r="AM163" s="6"/>
-      <c r="AN163" s="9"/>
-      <c r="AO163" s="6"/>
+      <c r="U163" s="9">
+        <v>0.20430107526881722</v>
+      </c>
+      <c r="V163" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="W163" s="9">
+        <v>0.021505376343999998</v>
+      </c>
+      <c r="X163" s="9">
+        <v>0.11827956989247312</v>
+      </c>
+      <c r="Y163" s="9">
+        <v>0.010752688172043012</v>
+      </c>
+      <c r="Z163" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA163" s="9">
+        <v>0.053763440860215055</v>
+      </c>
+      <c r="AB163" s="9">
+        <v>0.021505376344086023</v>
+      </c>
+      <c r="AC163" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD163" s="6">
+        <v>22</v>
+      </c>
+      <c r="AE163" s="6">
+        <v>19</v>
+      </c>
+      <c r="AF163" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG163" s="6">
+        <v>2</v>
+      </c>
+      <c r="AH163" s="6">
+        <v>11</v>
+      </c>
+      <c r="AI163" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ163" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK163" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL163" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM163" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN163" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO163" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP163" s="4">
         <v>58</v>
       </c>
@@ -25107,7 +25714,9 @@
       <c r="N164" s="6">
         <v>112</v>
       </c>
-      <c r="O164" s="6"/>
+      <c r="O164" s="6">
+        <v>65</v>
+      </c>
       <c r="P164" s="7">
         <v>5.4548672566371676</v>
       </c>
@@ -25117,31 +25726,75 @@
       <c r="R164" s="8">
         <v>5.3821631578947366</v>
       </c>
-      <c r="S164" s="8"/>
+      <c r="S164" s="8">
+        <v>7</v>
+      </c>
       <c r="T164" s="9">
         <v>0.36923076923076925</v>
       </c>
-      <c r="U164" s="9"/>
-      <c r="V164" s="9"/>
-      <c r="W164" s="9"/>
-      <c r="X164" s="9"/>
-      <c r="Y164" s="9"/>
-      <c r="Z164" s="9"/>
-      <c r="AA164" s="9"/>
-      <c r="AB164" s="9"/>
-      <c r="AC164" s="9"/>
-      <c r="AD164" s="6"/>
-      <c r="AE164" s="6"/>
-      <c r="AF164" s="6"/>
-      <c r="AG164" s="6"/>
-      <c r="AH164" s="6"/>
-      <c r="AI164" s="6"/>
-      <c r="AJ164" s="6"/>
-      <c r="AK164" s="6"/>
-      <c r="AL164" s="6"/>
-      <c r="AM164" s="6"/>
-      <c r="AN164" s="9"/>
-      <c r="AO164" s="6"/>
+      <c r="U164" s="9">
+        <v>0.18461538461538463</v>
+      </c>
+      <c r="V164" s="9">
+        <v>0</v>
+      </c>
+      <c r="W164" s="9">
+        <v>0.015384615383999999</v>
+      </c>
+      <c r="X164" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y164" s="9">
+        <v>0.030769230769230771</v>
+      </c>
+      <c r="Z164" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA164" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="AB164" s="9">
+        <v>0.015384615384615385</v>
+      </c>
+      <c r="AC164" s="9">
+        <v>0.030769230769230771</v>
+      </c>
+      <c r="AD164" s="6">
+        <v>15</v>
+      </c>
+      <c r="AE164" s="6">
+        <v>12</v>
+      </c>
+      <c r="AF164" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG164" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH164" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI164" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ164" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK164" s="6">
+        <v>10</v>
+      </c>
+      <c r="AL164" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM164" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN164" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO164" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP164" s="4">
         <v>58</v>
       </c>
@@ -27471,7 +28124,7 @@
         <v>19908</v>
       </c>
       <c r="B180" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C180" s="4">
         <v>51</v>
@@ -27501,35 +28154,93 @@
         <v>58</v>
       </c>
       <c r="L180" s="4"/>
-      <c r="M180" s="5"/>
-      <c r="N180" s="6"/>
-      <c r="O180" s="6"/>
-      <c r="P180" s="7"/>
-      <c r="Q180" s="8"/>
-      <c r="R180" s="8"/>
-      <c r="S180" s="8"/>
-      <c r="T180" s="9"/>
-      <c r="U180" s="9"/>
-      <c r="V180" s="9"/>
-      <c r="W180" s="9"/>
-      <c r="X180" s="9"/>
-      <c r="Y180" s="9"/>
-      <c r="Z180" s="9"/>
-      <c r="AA180" s="9"/>
-      <c r="AB180" s="9"/>
-      <c r="AC180" s="9"/>
-      <c r="AD180" s="6"/>
-      <c r="AE180" s="6"/>
-      <c r="AF180" s="6"/>
-      <c r="AG180" s="6"/>
-      <c r="AH180" s="6"/>
-      <c r="AI180" s="6"/>
-      <c r="AJ180" s="6"/>
-      <c r="AK180" s="6"/>
-      <c r="AL180" s="6"/>
-      <c r="AM180" s="6"/>
-      <c r="AN180" s="9"/>
-      <c r="AO180" s="6"/>
+      <c r="M180" s="5">
+        <v>4257.3400000000001</v>
+      </c>
+      <c r="N180" s="6">
+        <v>44</v>
+      </c>
+      <c r="O180" s="6">
+        <v>10</v>
+      </c>
+      <c r="P180" s="7">
+        <v>10.421111111111111</v>
+      </c>
+      <c r="Q180" s="8">
+        <v>37.948329999999999</v>
+      </c>
+      <c r="R180" s="8">
+        <v>18.61833</v>
+      </c>
+      <c r="S180" s="8">
+        <v>8</v>
+      </c>
+      <c r="T180" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="U180" s="9">
+        <v>0</v>
+      </c>
+      <c r="V180" s="9">
+        <v>0</v>
+      </c>
+      <c r="W180" s="9">
+        <v>0</v>
+      </c>
+      <c r="X180" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y180" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO180" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP180" s="4">
         <v>58</v>
       </c>
@@ -27606,7 +28317,9 @@
       <c r="N181" s="6">
         <v>46</v>
       </c>
-      <c r="O181" s="6"/>
+      <c r="O181" s="6">
+        <v>20</v>
+      </c>
       <c r="P181" s="7">
         <v>4.5041666666666664</v>
       </c>
@@ -27616,31 +28329,75 @@
       <c r="R181" s="8">
         <v>1.3518555555555556</v>
       </c>
-      <c r="S181" s="8"/>
+      <c r="S181" s="8">
+        <v>8</v>
+      </c>
       <c r="T181" s="9">
         <v>0.84999999999999998</v>
       </c>
-      <c r="U181" s="9"/>
-      <c r="V181" s="9"/>
-      <c r="W181" s="9"/>
-      <c r="X181" s="9"/>
-      <c r="Y181" s="9"/>
-      <c r="Z181" s="9"/>
-      <c r="AA181" s="9"/>
-      <c r="AB181" s="9"/>
-      <c r="AC181" s="9"/>
-      <c r="AD181" s="6"/>
-      <c r="AE181" s="6"/>
-      <c r="AF181" s="6"/>
-      <c r="AG181" s="6"/>
-      <c r="AH181" s="6"/>
-      <c r="AI181" s="6"/>
-      <c r="AJ181" s="6"/>
-      <c r="AK181" s="6"/>
-      <c r="AL181" s="6"/>
-      <c r="AM181" s="6"/>
-      <c r="AN181" s="9"/>
-      <c r="AO181" s="6"/>
+      <c r="U181" s="9">
+        <v>0.65000000000000002</v>
+      </c>
+      <c r="V181" s="9">
+        <v>0</v>
+      </c>
+      <c r="W181" s="9">
+        <v>0</v>
+      </c>
+      <c r="X181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="9">
+        <v>0.65000000000000002</v>
+      </c>
+      <c r="AB181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD181" s="6">
+        <v>13</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK181" s="6">
+        <v>13</v>
+      </c>
+      <c r="AL181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO181" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP181" s="4">
         <v>58</v>
       </c>
@@ -28758,7 +29515,9 @@
       <c r="N189" s="6">
         <v>82</v>
       </c>
-      <c r="O189" s="6"/>
+      <c r="O189" s="6">
+        <v>70</v>
+      </c>
       <c r="P189" s="7">
         <v>7.1579268292682929</v>
       </c>
@@ -28768,31 +29527,75 @@
       <c r="R189" s="8">
         <v>15.393988524590165</v>
       </c>
-      <c r="S189" s="8"/>
+      <c r="S189" s="8">
+        <v>7</v>
+      </c>
       <c r="T189" s="9">
         <v>0.22857142857142856</v>
       </c>
-      <c r="U189" s="9"/>
-      <c r="V189" s="9"/>
-      <c r="W189" s="9"/>
-      <c r="X189" s="9"/>
-      <c r="Y189" s="9"/>
-      <c r="Z189" s="9"/>
-      <c r="AA189" s="9"/>
-      <c r="AB189" s="9"/>
-      <c r="AC189" s="9"/>
-      <c r="AD189" s="6"/>
-      <c r="AE189" s="6"/>
-      <c r="AF189" s="6"/>
-      <c r="AG189" s="6"/>
-      <c r="AH189" s="6"/>
-      <c r="AI189" s="6"/>
-      <c r="AJ189" s="6"/>
-      <c r="AK189" s="6"/>
-      <c r="AL189" s="6"/>
-      <c r="AM189" s="6"/>
-      <c r="AN189" s="9"/>
-      <c r="AO189" s="6"/>
+      <c r="U189" s="9">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="V189" s="9">
+        <v>0</v>
+      </c>
+      <c r="W189" s="9">
+        <v>0</v>
+      </c>
+      <c r="X189" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="Y189" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="Z189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA189" s="9">
+        <v>0.15714285714285714</v>
+      </c>
+      <c r="AB189" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="AC189" s="9">
+        <v>0.58571428571428574</v>
+      </c>
+      <c r="AD189" s="6">
+        <v>55</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>50</v>
+      </c>
+      <c r="AF189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK189" s="6">
+        <v>11</v>
+      </c>
+      <c r="AL189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM189" s="6">
+        <v>41</v>
+      </c>
+      <c r="AN189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO189" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP189" s="4">
         <v>58</v>
       </c>
@@ -28869,7 +29672,9 @@
       <c r="N190" s="6">
         <v>66</v>
       </c>
-      <c r="O190" s="6"/>
+      <c r="O190" s="6">
+        <v>27</v>
+      </c>
       <c r="P190" s="7">
         <v>3.7413983870967744</v>
       </c>
@@ -28879,31 +29684,75 @@
       <c r="R190" s="8">
         <v>3.0566680000000002</v>
       </c>
-      <c r="S190" s="8"/>
+      <c r="S190" s="8">
+        <v>7</v>
+      </c>
       <c r="T190" s="9">
         <v>0.70370370370370372</v>
       </c>
-      <c r="U190" s="9"/>
-      <c r="V190" s="9"/>
-      <c r="W190" s="9"/>
-      <c r="X190" s="9"/>
-      <c r="Y190" s="9"/>
-      <c r="Z190" s="9"/>
-      <c r="AA190" s="9"/>
-      <c r="AB190" s="9"/>
-      <c r="AC190" s="9"/>
-      <c r="AD190" s="6"/>
-      <c r="AE190" s="6"/>
-      <c r="AF190" s="6"/>
-      <c r="AG190" s="6"/>
-      <c r="AH190" s="6"/>
-      <c r="AI190" s="6"/>
-      <c r="AJ190" s="6"/>
-      <c r="AK190" s="6"/>
-      <c r="AL190" s="6"/>
-      <c r="AM190" s="6"/>
-      <c r="AN190" s="9"/>
-      <c r="AO190" s="6"/>
+      <c r="U190" s="9">
+        <v>0.25925925925925924</v>
+      </c>
+      <c r="V190" s="9">
+        <v>0</v>
+      </c>
+      <c r="W190" s="9">
+        <v>0</v>
+      </c>
+      <c r="X190" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="Y190" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AB190" s="9">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="AC190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD190" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH190" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK190" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO190" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP190" s="4">
         <v>58</v>
       </c>
@@ -31374,7 +32223,9 @@
       <c r="N207" s="6">
         <v>49</v>
       </c>
-      <c r="O207" s="6"/>
+      <c r="O207" s="6">
+        <v>23</v>
+      </c>
       <c r="P207" s="7">
         <v>13.009375</v>
       </c>
@@ -31384,31 +32235,75 @@
       <c r="R207" s="8">
         <v>20.873486363636363</v>
       </c>
-      <c r="S207" s="8"/>
+      <c r="S207" s="8">
+        <v>7</v>
+      </c>
       <c r="T207" s="9">
         <v>0.043478260869565216</v>
       </c>
-      <c r="U207" s="9"/>
-      <c r="V207" s="9"/>
-      <c r="W207" s="9"/>
-      <c r="X207" s="9"/>
-      <c r="Y207" s="9"/>
-      <c r="Z207" s="9"/>
-      <c r="AA207" s="9"/>
-      <c r="AB207" s="9"/>
-      <c r="AC207" s="9"/>
-      <c r="AD207" s="6"/>
-      <c r="AE207" s="6"/>
-      <c r="AF207" s="6"/>
-      <c r="AG207" s="6"/>
-      <c r="AH207" s="6"/>
-      <c r="AI207" s="6"/>
-      <c r="AJ207" s="6"/>
-      <c r="AK207" s="6"/>
-      <c r="AL207" s="6"/>
-      <c r="AM207" s="6"/>
-      <c r="AN207" s="9"/>
-      <c r="AO207" s="6"/>
+      <c r="U207" s="9">
+        <v>0.2608695652173913</v>
+      </c>
+      <c r="V207" s="9">
+        <v>0</v>
+      </c>
+      <c r="W207" s="9">
+        <v>0</v>
+      </c>
+      <c r="X207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="AB207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC207" s="9">
+        <v>0.21739130434782608</v>
+      </c>
+      <c r="AD207" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK207" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM207" s="6">
+        <v>5</v>
+      </c>
+      <c r="AN207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO207" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP207" s="4">
         <v>58</v>
       </c>
@@ -32407,52 +33302,52 @@
         <v>321</v>
       </c>
       <c t="s" r="Z216" s="11">
+        <v>319</v>
+      </c>
+      <c t="s" r="AA216" s="11">
         <v>322</v>
       </c>
-      <c t="s" r="AA216" s="11">
+      <c t="s" r="AB216" s="11">
         <v>323</v>
       </c>
-      <c t="s" r="AB216" s="11">
+      <c t="s" r="AC216" s="11">
         <v>324</v>
       </c>
-      <c t="s" r="AC216" s="11">
+      <c t="s" r="AD216" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AD216" s="11">
+      <c t="s" r="AE216" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AE216" s="11">
+      <c t="s" r="AF216" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AF216" s="11">
+      <c t="s" r="AG216" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AG216" s="11">
+      <c t="s" r="AH216" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AH216" s="11">
+      <c t="s" r="AI216" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AI216" s="11">
+      <c t="s" r="AJ216" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AJ216" s="11">
+      <c t="s" r="AK216" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AK216" s="11">
+      <c t="s" r="AL216" s="11">
         <v>333</v>
       </c>
-      <c t="s" r="AL216" s="11">
+      <c t="s" r="AM216" s="11">
         <v>334</v>
       </c>
-      <c t="s" r="AM216" s="11">
+      <c t="s" r="AN216" s="11">
         <v>335</v>
       </c>
-      <c t="s" r="AN216" s="11">
+      <c t="s" r="AO216" s="11">
         <v>336</v>
-      </c>
-      <c t="s" r="AO216" s="11">
-        <v>337</v>
       </c>
       <c r="AP216" s="12"/>
       <c t="s" r="AQ216" s="12">
@@ -32469,10 +33364,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX216" s="11">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c t="s" r="AY216" s="11">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AZ216" s="12"/>
       <c r="BA216" s="12"/>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-10).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-10).xlsx
@@ -932,91 +932,94 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
   </si>
   <si>
-    <t>33</t>
+    <t>215</t>
   </si>
   <si>
-    <t>R$ 8.662,59</t>
+    <t>30</t>
   </si>
   <si>
-    <t>91.0</t>
+    <t>R$ 8.656,60</t>
   </si>
   <si>
-    <t>56.9</t>
+    <t>91.1</t>
   </si>
   <si>
-    <t>6.10</t>
+    <t>57.1</t>
   </si>
   <si>
-    <t>20.8</t>
+    <t>6.09</t>
+  </si>
+  <si>
+    <t>20.7</t>
   </si>
   <si>
     <t>8.0</t>
   </si>
   <si>
-    <t>6.1</t>
+    <t>6.3</t>
   </si>
   <si>
-    <t>37.6%</t>
+    <t>37.1%</t>
   </si>
   <si>
     <t>17.1%</t>
   </si>
   <si>
-    <t>1.4%</t>
+    <t>1.3%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>3.3%</t>
+    <t>3.2%</t>
   </si>
   <si>
-    <t>1.1%</t>
+    <t>1.0%</t>
   </si>
   <si>
-    <t>5.8%</t>
+    <t>6.0%</t>
   </si>
   <si>
     <t>2.8%</t>
   </si>
   <si>
-    <t>5.5%</t>
+    <t>5.6%</t>
   </si>
   <si>
-    <t>2109.0</t>
+    <t>2200.0</t>
   </si>
   <si>
-    <t>1768.0</t>
+    <t>1836.0</t>
   </si>
   <si>
-    <t>140.0</t>
+    <t>141.0</t>
+  </si>
+  <si>
+    <t>20.0</t>
+  </si>
+  <si>
+    <t>343.0</t>
+  </si>
+  <si>
+    <t>110.0</t>
   </si>
   <si>
     <t>19.0</t>
   </si>
   <si>
-    <t>341.0</t>
+    <t>649.0</t>
   </si>
   <si>
-    <t>109.0</t>
+    <t>303.0</t>
   </si>
   <si>
-    <t>18.0</t>
+    <t>598.0</t>
   </si>
   <si>
-    <t>606.0</t>
-  </si>
-  <si>
-    <t>285.0</t>
-  </si>
-  <si>
-    <t>573.0</t>
-  </si>
-  <si>
-    <t>0.4%</t>
+    <t>0.3%</t>
   </si>
   <si>
     <t>37.0</t>
@@ -6468,7 +6471,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>51</v>
@@ -6498,35 +6501,93 @@
         <v>58</v>
       </c>
       <c r="L34" s="4"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9"/>
-      <c r="Y34" s="9"/>
-      <c r="Z34" s="9"/>
-      <c r="AA34" s="9"/>
-      <c r="AB34" s="9"/>
-      <c r="AC34" s="9"/>
-      <c r="AD34" s="6"/>
-      <c r="AE34" s="6"/>
-      <c r="AF34" s="6"/>
-      <c r="AG34" s="6"/>
-      <c r="AH34" s="6"/>
-      <c r="AI34" s="6"/>
-      <c r="AJ34" s="6"/>
-      <c r="AK34" s="6"/>
-      <c r="AL34" s="6"/>
-      <c r="AM34" s="6"/>
-      <c r="AN34" s="9"/>
-      <c r="AO34" s="6"/>
+      <c r="M34" s="5">
+        <v>13650.41</v>
+      </c>
+      <c r="N34" s="6">
+        <v>158</v>
+      </c>
+      <c r="O34" s="6">
+        <v>114</v>
+      </c>
+      <c r="P34" s="7">
+        <v>9.688486842105263</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>18.336842105263159</v>
+      </c>
+      <c r="R34" s="8">
+        <v>2.8475972972972974</v>
+      </c>
+      <c r="S34" s="8">
+        <v>6</v>
+      </c>
+      <c r="T34" s="9">
+        <v>0.45614035087719296</v>
+      </c>
+      <c r="U34" s="9">
+        <v>0.45614035087719296</v>
+      </c>
+      <c r="V34" s="9">
+        <v>0</v>
+      </c>
+      <c r="W34" s="9">
+        <v>0</v>
+      </c>
+      <c r="X34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="9">
+        <v>0.008771929824561403</v>
+      </c>
+      <c r="AA34" s="9">
+        <v>0.34210526315789475</v>
+      </c>
+      <c r="AB34" s="9">
+        <v>0.13157894736842105</v>
+      </c>
+      <c r="AC34" s="9">
+        <v>0.14035087719298245</v>
+      </c>
+      <c r="AD34" s="6">
+        <v>71</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>52</v>
+      </c>
+      <c r="AF34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK34" s="6">
+        <v>39</v>
+      </c>
+      <c r="AL34" s="6">
+        <v>15</v>
+      </c>
+      <c r="AM34" s="6">
+        <v>16</v>
+      </c>
+      <c r="AN34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP34" s="4">
         <v>58</v>
       </c>
@@ -6724,7 +6785,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6754,35 +6815,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>5480.9200000000001</v>
+      </c>
+      <c r="N36" s="6">
+        <v>58</v>
+      </c>
+      <c r="O36" s="6">
+        <v>48</v>
+      </c>
+      <c r="P36" s="7">
+        <v>5.065847540983607</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>20.465624999999999</v>
+      </c>
+      <c r="R36" s="8">
+        <v>8.9010638297872351</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -12684,7 +12803,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12712,35 +12831,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>9694.0699999999997</v>
+      </c>
+      <c r="N76" s="6">
+        <v>107</v>
+      </c>
+      <c r="O76" s="6">
+        <v>54</v>
+      </c>
+      <c r="P76" s="7">
+        <v>3.8773584905660377</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>22.857407407407408</v>
+      </c>
+      <c r="R76" s="8">
+        <v>9.6234574074074075</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.092592592592592587</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0.092592592592592587</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>5</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -18558,33 +18735,79 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
       <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
+      <c r="O116" s="6">
+        <v>39</v>
+      </c>
       <c r="P116" s="7"/>
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
-      <c r="S116" s="8"/>
+      <c r="S116" s="8">
+        <v>7</v>
+      </c>
       <c r="T116" s="9"/>
-      <c r="U116" s="9"/>
-      <c r="V116" s="9"/>
-      <c r="W116" s="9"/>
-      <c r="X116" s="9"/>
-      <c r="Y116" s="9"/>
-      <c r="Z116" s="9"/>
-      <c r="AA116" s="9"/>
-      <c r="AB116" s="9"/>
-      <c r="AC116" s="9"/>
-      <c r="AD116" s="6"/>
-      <c r="AE116" s="6"/>
-      <c r="AF116" s="6"/>
-      <c r="AG116" s="6"/>
-      <c r="AH116" s="6"/>
-      <c r="AI116" s="6"/>
-      <c r="AJ116" s="6"/>
-      <c r="AK116" s="6"/>
-      <c r="AL116" s="6"/>
-      <c r="AM116" s="6"/>
-      <c r="AN116" s="9"/>
-      <c r="AO116" s="6"/>
+      <c r="U116" s="9">
+        <v>0.10256410256410256</v>
+      </c>
+      <c r="V116" s="9">
+        <v>0.02564102564102564</v>
+      </c>
+      <c r="W116" s="9">
+        <v>0</v>
+      </c>
+      <c r="X116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="9">
+        <v>0.02564102564102564</v>
+      </c>
+      <c r="AB116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="9">
+        <v>0.05128205128205128</v>
+      </c>
+      <c r="AD116" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE116" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF116" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM116" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO116" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP116" s="4">
         <v>58</v>
       </c>
@@ -22325,7 +22548,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>51</v>
@@ -22355,35 +22578,93 @@
         <v>58</v>
       </c>
       <c r="L141" s="4"/>
-      <c r="M141" s="5"/>
-      <c r="N141" s="6"/>
-      <c r="O141" s="6"/>
-      <c r="P141" s="7"/>
-      <c r="Q141" s="8"/>
-      <c r="R141" s="8"/>
-      <c r="S141" s="8"/>
-      <c r="T141" s="9"/>
-      <c r="U141" s="9"/>
-      <c r="V141" s="9"/>
-      <c r="W141" s="9"/>
-      <c r="X141" s="9"/>
-      <c r="Y141" s="9"/>
-      <c r="Z141" s="9"/>
-      <c r="AA141" s="9"/>
-      <c r="AB141" s="9"/>
-      <c r="AC141" s="9"/>
-      <c r="AD141" s="6"/>
-      <c r="AE141" s="6"/>
-      <c r="AF141" s="6"/>
-      <c r="AG141" s="6"/>
-      <c r="AH141" s="6"/>
-      <c r="AI141" s="6"/>
-      <c r="AJ141" s="6"/>
-      <c r="AK141" s="6"/>
-      <c r="AL141" s="6"/>
-      <c r="AM141" s="6"/>
-      <c r="AN141" s="9"/>
-      <c r="AO141" s="6"/>
+      <c r="M141" s="5">
+        <v>4722.5600000000004</v>
+      </c>
+      <c r="N141" s="6">
+        <v>58</v>
+      </c>
+      <c r="O141" s="6">
+        <v>27</v>
+      </c>
+      <c r="P141" s="7">
+        <v>3.0519230769230767</v>
+      </c>
+      <c r="Q141" s="8">
+        <v>13.117285185185185</v>
+      </c>
+      <c r="R141" s="8">
+        <v>2.091974074074074</v>
+      </c>
+      <c r="S141" s="8">
+        <v>8</v>
+      </c>
+      <c r="T141" s="9">
+        <v>0.85185185185185186</v>
+      </c>
+      <c r="U141" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="V141" s="9">
+        <v>0</v>
+      </c>
+      <c r="W141" s="9">
+        <v>0</v>
+      </c>
+      <c r="X141" s="9">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="Y141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB141" s="9">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="AC141" s="9">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="AD141" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM141" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO141" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP141" s="4">
         <v>58</v>
       </c>
@@ -33246,137 +33527,282 @@
       </c>
     </row>
     <row r="216" ht="13.5" customHeight="1">
-      <c t="s" r="A216" s="11">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>56</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>57</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>58</v>
+      </c>
+      <c r="L216" s="4"/>
+      <c r="M216" s="5"/>
+      <c r="N216" s="6"/>
+      <c r="O216" s="6">
+        <v>90</v>
+      </c>
+      <c r="P216" s="7"/>
+      <c r="Q216" s="8"/>
+      <c r="R216" s="8"/>
+      <c r="S216" s="8">
+        <v>7</v>
+      </c>
+      <c r="T216" s="9"/>
+      <c r="U216" s="9">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="V216" s="9">
+        <v>0</v>
+      </c>
+      <c r="W216" s="9">
+        <v>0.011111111111000001</v>
+      </c>
+      <c r="X216" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y216" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA216" s="9">
+        <v>0.022222222222222223</v>
+      </c>
+      <c r="AB216" s="9">
+        <v>0.011111111111111112</v>
+      </c>
+      <c r="AC216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD216" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE216" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK216" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO216" s="6">
+        <v>0</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>58</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>307</v>
       </c>
-      <c t="s" r="B216" s="11">
+      <c t="s" r="AS216" s="4">
+        <v>60</v>
+      </c>
+      <c t="s" r="AT216" s="4">
+        <v>61</v>
+      </c>
+      <c t="s" r="AU216" s="4">
+        <v>62</v>
+      </c>
+      <c t="s" r="AV216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW216" s="4">
+        <v>59</v>
+      </c>
+      <c r="AX216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ216" s="10"/>
+      <c t="s" r="BA216" s="4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="217" ht="13.5" customHeight="1">
+      <c t="s" r="A217" s="11">
         <v>308</v>
       </c>
-      <c r="C216" s="12"/>
-      <c r="D216" s="12"/>
-      <c r="E216" s="12"/>
-      <c r="F216" s="12"/>
-      <c r="G216" s="12"/>
-      <c r="H216" s="12"/>
-      <c r="I216" s="12"/>
-      <c r="J216" s="12"/>
-      <c r="K216" s="12"/>
-      <c r="L216" s="12"/>
-      <c t="s" r="M216" s="11">
+      <c t="s" r="B217" s="11">
         <v>309</v>
       </c>
-      <c t="s" r="N216" s="11">
+      <c r="C217" s="12"/>
+      <c r="D217" s="12"/>
+      <c r="E217" s="12"/>
+      <c r="F217" s="12"/>
+      <c r="G217" s="12"/>
+      <c r="H217" s="12"/>
+      <c r="I217" s="12"/>
+      <c r="J217" s="12"/>
+      <c r="K217" s="12"/>
+      <c r="L217" s="12"/>
+      <c t="s" r="M217" s="11">
         <v>310</v>
       </c>
-      <c t="s" r="O216" s="11">
+      <c t="s" r="N217" s="11">
         <v>311</v>
       </c>
-      <c t="s" r="P216" s="11">
+      <c t="s" r="O217" s="11">
         <v>312</v>
       </c>
-      <c t="s" r="Q216" s="11">
+      <c t="s" r="P217" s="11">
         <v>313</v>
       </c>
-      <c t="s" r="R216" s="11">
+      <c t="s" r="Q217" s="11">
         <v>314</v>
       </c>
-      <c t="s" r="S216" s="11">
+      <c t="s" r="R217" s="11">
         <v>315</v>
       </c>
-      <c t="s" r="T216" s="11">
+      <c t="s" r="S217" s="11">
         <v>316</v>
       </c>
-      <c t="s" r="U216" s="11">
+      <c t="s" r="T217" s="11">
         <v>317</v>
       </c>
-      <c t="s" r="V216" s="11">
+      <c t="s" r="U217" s="11">
         <v>318</v>
       </c>
-      <c t="s" r="W216" s="11">
+      <c t="s" r="V217" s="11">
         <v>319</v>
       </c>
-      <c t="s" r="X216" s="11">
+      <c t="s" r="W217" s="11">
         <v>320</v>
       </c>
-      <c t="s" r="Y216" s="11">
+      <c t="s" r="X217" s="11">
         <v>321</v>
       </c>
-      <c t="s" r="Z216" s="11">
-        <v>319</v>
-      </c>
-      <c t="s" r="AA216" s="11">
+      <c t="s" r="Y217" s="11">
         <v>322</v>
       </c>
-      <c t="s" r="AB216" s="11">
+      <c t="s" r="Z217" s="11">
+        <v>320</v>
+      </c>
+      <c t="s" r="AA217" s="11">
         <v>323</v>
       </c>
-      <c t="s" r="AC216" s="11">
+      <c t="s" r="AB217" s="11">
         <v>324</v>
       </c>
-      <c t="s" r="AD216" s="11">
+      <c t="s" r="AC217" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AE216" s="11">
+      <c t="s" r="AD217" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AF216" s="11">
+      <c t="s" r="AE217" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AG216" s="11">
+      <c t="s" r="AF217" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AH216" s="11">
+      <c t="s" r="AG217" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AI216" s="11">
+      <c t="s" r="AH217" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AJ216" s="11">
+      <c t="s" r="AI217" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AK216" s="11">
+      <c t="s" r="AJ217" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AL216" s="11">
+      <c t="s" r="AK217" s="11">
         <v>333</v>
       </c>
-      <c t="s" r="AM216" s="11">
+      <c t="s" r="AL217" s="11">
         <v>334</v>
       </c>
-      <c t="s" r="AN216" s="11">
+      <c t="s" r="AM217" s="11">
         <v>335</v>
       </c>
-      <c t="s" r="AO216" s="11">
+      <c t="s" r="AN217" s="11">
         <v>336</v>
       </c>
-      <c r="AP216" s="12"/>
-      <c t="s" r="AQ216" s="12">
-        <v>59</v>
-      </c>
-      <c r="AR216" s="12"/>
-      <c r="AS216" s="12"/>
-      <c r="AT216" s="12"/>
-      <c r="AU216" s="12"/>
-      <c t="s" r="AV216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AW216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AX216" s="11">
+      <c t="s" r="AO217" s="11">
         <v>337</v>
       </c>
-      <c t="s" r="AY216" s="11">
-        <v>337</v>
-      </c>
-      <c r="AZ216" s="12"/>
-      <c r="BA216" s="12"/>
+      <c r="AP217" s="12"/>
+      <c t="s" r="AQ217" s="12">
+        <v>59</v>
+      </c>
+      <c r="AR217" s="12"/>
+      <c r="AS217" s="12"/>
+      <c r="AT217" s="12"/>
+      <c r="AU217" s="12"/>
+      <c t="s" r="AV217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AX217" s="11">
+        <v>338</v>
+      </c>
+      <c t="s" r="AY217" s="11">
+        <v>338</v>
+      </c>
+      <c r="AZ217" s="12"/>
+      <c r="BA217" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:BA216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:BA217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-10).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-10).xlsx
@@ -938,13 +938,13 @@
     <t>215</t>
   </si>
   <si>
-    <t>30</t>
+    <t>29</t>
   </si>
   <si>
-    <t>R$ 8.656,60</t>
+    <t>R$ 8.668,25</t>
   </si>
   <si>
-    <t>91.1</t>
+    <t>91.2</t>
   </si>
   <si>
     <t>57.1</t>
@@ -956,13 +956,13 @@
     <t>20.7</t>
   </si>
   <si>
-    <t>8.0</t>
+    <t>7.9</t>
   </si>
   <si>
     <t>6.3</t>
   </si>
   <si>
-    <t>37.1%</t>
+    <t>37.3%</t>
   </si>
   <si>
     <t>17.1%</t>
@@ -25192,7 +25192,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>51</v>
@@ -25222,18 +25222,30 @@
         <v>58</v>
       </c>
       <c r="L159" s="4"/>
-      <c r="M159" s="5"/>
-      <c r="N159" s="6"/>
+      <c r="M159" s="5">
+        <v>10810.469999999999</v>
+      </c>
+      <c r="N159" s="6">
+        <v>105</v>
+      </c>
       <c r="O159" s="6">
         <v>88</v>
       </c>
-      <c r="P159" s="7"/>
-      <c r="Q159" s="8"/>
-      <c r="R159" s="8"/>
+      <c r="P159" s="7">
+        <v>6.763461538461538</v>
+      </c>
+      <c r="Q159" s="8">
+        <v>20.188068181818181</v>
+      </c>
+      <c r="R159" s="8">
+        <v>6.5725494117647054</v>
+      </c>
       <c r="S159" s="8">
         <v>7</v>
       </c>
-      <c r="T159" s="9"/>
+      <c r="T159" s="9">
+        <v>0.22727272727272727</v>
+      </c>
       <c r="U159" s="9">
         <v>0.045454545454545456</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-10).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-10).xlsx
@@ -938,10 +938,10 @@
     <t>215</t>
   </si>
   <si>
-    <t>29</t>
+    <t>28</t>
   </si>
   <si>
-    <t>R$ 8.668,25</t>
+    <t>R$ 8.676,87</t>
   </si>
   <si>
     <t>91.2</t>
@@ -950,19 +950,19 @@
     <t>57.1</t>
   </si>
   <si>
-    <t>6.09</t>
+    <t>6.11</t>
   </si>
   <si>
-    <t>20.7</t>
+    <t>20.8</t>
   </si>
   <si>
-    <t>7.9</t>
+    <t>8.0</t>
   </si>
   <si>
     <t>6.3</t>
   </si>
   <si>
-    <t>37.3%</t>
+    <t>37.4%</t>
   </si>
   <si>
     <t>17.1%</t>
@@ -14776,7 +14776,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14804,14 +14804,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>10272.5</v>
+      </c>
+      <c r="N89" s="6">
+        <v>90</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>10.24945054945055</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>27.457446808510639</v>
+      </c>
+      <c r="R89" s="8">
+        <v>10.408139534883722</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.1702127659574468</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -29202,7 +29214,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>51</v>
@@ -31910,7 +31922,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>51</v>
@@ -33543,7 +33555,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>51</v>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-10).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-10).xlsx
@@ -938,34 +938,34 @@
     <t>215</t>
   </si>
   <si>
-    <t>28</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 8.676,87</t>
+    <t>R$ 8.681,50</t>
   </si>
   <si>
-    <t>91.2</t>
+    <t>91.0</t>
   </si>
   <si>
-    <t>57.1</t>
+    <t>57.7</t>
   </si>
   <si>
-    <t>6.11</t>
+    <t>6.17</t>
   </si>
   <si>
     <t>20.8</t>
   </si>
   <si>
-    <t>8.0</t>
+    <t>7.9</t>
   </si>
   <si>
-    <t>6.3</t>
+    <t>6.5</t>
   </si>
   <si>
-    <t>37.4%</t>
+    <t>37.1%</t>
   </si>
   <si>
-    <t>17.1%</t>
+    <t>16.6%</t>
   </si>
   <si>
     <t>1.3%</t>
@@ -974,34 +974,34 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>3.2%</t>
+    <t>3.1%</t>
   </si>
   <si>
     <t>1.0%</t>
   </si>
   <si>
-    <t>6.0%</t>
+    <t>5.8%</t>
   </si>
   <si>
-    <t>2.8%</t>
+    <t>2.7%</t>
   </si>
   <si>
-    <t>5.6%</t>
+    <t>5.4%</t>
   </si>
   <si>
-    <t>2200.0</t>
+    <t>2223.0</t>
   </si>
   <si>
-    <t>1836.0</t>
+    <t>1858.0</t>
   </si>
   <si>
-    <t>141.0</t>
+    <t>143.0</t>
   </si>
   <si>
     <t>20.0</t>
   </si>
   <si>
-    <t>343.0</t>
+    <t>349.0</t>
   </si>
   <si>
     <t>110.0</t>
@@ -1010,13 +1010,13 @@
     <t>19.0</t>
   </si>
   <si>
-    <t>649.0</t>
+    <t>651.0</t>
   </si>
   <si>
-    <t>303.0</t>
+    <t>306.0</t>
   </si>
   <si>
-    <t>598.0</t>
+    <t>608.0</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -2209,7 +2209,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2239,35 +2239,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>14195.23</v>
+      </c>
+      <c r="N6" s="6">
+        <v>136</v>
+      </c>
+      <c r="O6" s="6">
+        <v>101</v>
+      </c>
+      <c r="P6" s="7">
+        <v>6.4232589552238801</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>15.415511881188118</v>
+      </c>
+      <c r="R6" s="8">
+        <v>1.7801980198019802</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.58415841584158412</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.029702970297029702</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.029702970297029702</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -9132,7 +9190,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9162,14 +9220,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>1457.3499999999999</v>
+      </c>
+      <c r="N51" s="6">
+        <v>17</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>5.0235294117647058</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>20.616671428571429</v>
+      </c>
+      <c r="R51" s="8">
+        <v>13.199999999999999</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0.42857142857142855</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -10201,33 +10271,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>91</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.02197802197802198</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.032967032967032968</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0.087912087912087919</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>13</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -24124,7 +24240,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -24154,35 +24270,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>8006.25</v>
+      </c>
+      <c r="N151" s="6">
+        <v>84</v>
+      </c>
+      <c r="O151" s="6">
+        <v>70</v>
+      </c>
+      <c r="P151" s="7">
+        <v>6.2089285714285705</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>15.799761428571429</v>
+      </c>
+      <c r="R151" s="8">
+        <v>2.9007246376811593</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.47142857142857142</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.042857142857142858</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -25006,7 +25180,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -25036,35 +25210,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>8290.4500000000007</v>
+      </c>
+      <c r="N157" s="6">
+        <v>86</v>
+      </c>
+      <c r="O157" s="6">
+        <v>71</v>
+      </c>
+      <c r="P157" s="7">
+        <v>13.166084883720931</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>30.335915492957746</v>
+      </c>
+      <c r="R157" s="8">
+        <v>9.1659619718309866</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.14084507042253522</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -25105,7 +25337,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25135,35 +25367,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>8659.4400000000005</v>
+      </c>
+      <c r="N158" s="6">
+        <v>83</v>
+      </c>
+      <c r="O158" s="6">
+        <v>72</v>
+      </c>
+      <c r="P158" s="7">
+        <v>9.3335365853658541</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>24.177777777777777</v>
+      </c>
+      <c r="R158" s="8">
+        <v>7.6877319444444447</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -26140,7 +26430,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26170,35 +26460,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>12341.02</v>
+      </c>
+      <c r="N165" s="6">
+        <v>114</v>
+      </c>
+      <c r="O165" s="6">
+        <v>56</v>
+      </c>
+      <c r="P165" s="7">
+        <v>7.6494097345132737</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>16.961607142857144</v>
+      </c>
+      <c r="R165" s="8">
+        <v>3.3333339285714283</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0.053571428571428568</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
